--- a/StructureDefinition-openimis-coverage.xlsx
+++ b/StructureDefinition-openimis-coverage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-26T15:39:34+00:00</t>
+    <t>2025-09-08T11:14:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -9327,7 +9327,7 @@
         <v>81</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>22</v>
@@ -9569,7 +9569,7 @@
         <v>81</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>22</v>
@@ -9691,7 +9691,7 @@
         <v>81</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>22</v>
@@ -9931,7 +9931,7 @@
         <v>81</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>22</v>
@@ -10053,7 +10053,7 @@
         <v>81</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>22</v>
@@ -11741,7 +11741,7 @@
         <v>81</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>22</v>
@@ -11861,7 +11861,7 @@
         <v>81</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>22</v>
@@ -11981,7 +11981,7 @@
         <v>81</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>22</v>
@@ -13901,7 +13901,7 @@
         <v>81</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>22</v>
@@ -14023,7 +14023,7 @@
         <v>81</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>22</v>

--- a/StructureDefinition-openimis-coverage.xlsx
+++ b/StructureDefinition-openimis-coverage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-08T11:14:40+00:00</t>
+    <t>2025-09-08T11:37:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-openimis-coverage.xlsx
+++ b/StructureDefinition-openimis-coverage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-08T11:37:47+00:00</t>
+    <t>2025-09-08T11:49:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
